--- a/public/templates/tamplate_jadwal_ecogreen.xlsx
+++ b/public/templates/tamplate_jadwal_ecogreen.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\e-OutSourcing\E-outsourcing-trpl210\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C2428C4-454E-4910-A4B6-867E1755F4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B92C7E-CDEA-4589-8CE4-4BE5A767301F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0396C9FC-5386-43A1-BEFB-9FD9F18D1A27}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
+    <sheet name="Aturan Membuat Jadwal" sheetId="2" r:id="rId1"/>
+    <sheet name="Atur Jadwal" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,13 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>PRIODE 05/11 2024</t>
-  </si>
-  <si>
-    <t>13/19 JAN 2025</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>No</t>
   </si>
@@ -66,9 +61,6 @@
     <t>PT ECOGREEN OLEOCHEMICALS</t>
   </si>
   <si>
-    <t>WEEKLY SCEDHULE</t>
-  </si>
-  <si>
     <t>cara penggunaan</t>
   </si>
   <si>
@@ -81,17 +73,44 @@
     <t xml:space="preserve">isi kolom kolom tanggal sesuai dengan tipe kehadiran karyawan </t>
   </si>
   <si>
-    <t>shift: pagi = p, sore =s, malam = m</t>
-  </si>
-  <si>
-    <t>cuti = c, izin = I</t>
+    <t>SCHEDULE EMPLOYEE</t>
+  </si>
+  <si>
+    <t>PERIODE</t>
+  </si>
+  <si>
+    <t>torik</t>
+  </si>
+  <si>
+    <t>Rangga</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>shift: pagi = p, sore =s, malam = m cuti = c</t>
+  </si>
+  <si>
+    <t>CONTOH PENGGUNAAN, JIKA INGIN MENGISI JADWAL GUNAKAN SHEET " ATUR JADWA "</t>
+  </si>
+  <si>
+    <t>jangan menambah baris baru pada sheet atur jadwal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +135,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -148,8 +182,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -263,65 +333,95 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -338,49 +438,103 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{11E472FD-6229-4709-A99D-206DC1B2C2A5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -691,391 +845,345 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD061106-7AC9-44E9-949E-0B9372A6C704}">
-  <dimension ref="A1:M54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35229D1-C8A4-48A2-98D5-9676AA268EB8}">
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33"/>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="21">
+        <v>45670</v>
+      </c>
+      <c r="D11" s="21">
+        <v>45671</v>
+      </c>
+      <c r="E11" s="21">
+        <v>45672</v>
+      </c>
+      <c r="F11" s="22">
+        <v>45673</v>
+      </c>
+      <c r="G11" s="21">
+        <v>45674</v>
+      </c>
+      <c r="H11" s="21">
+        <v>45675</v>
+      </c>
+      <c r="I11" s="21">
+        <v>45676</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>1</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="C12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>2</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="C13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-    </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="E13" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
         <v>3</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="12">
-        <v>45670</v>
-      </c>
-      <c r="D14" s="12">
-        <v>45671</v>
-      </c>
-      <c r="E14" s="12">
-        <v>45672</v>
-      </c>
-      <c r="F14" s="15">
-        <v>45673</v>
-      </c>
-      <c r="G14" s="12">
-        <v>45674</v>
-      </c>
-      <c r="H14" s="12">
-        <v>45675</v>
-      </c>
-      <c r="I14" s="12">
-        <v>45676</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>1</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
-        <v>2</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>3</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="16"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="16"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD061106-7AC9-44E9-949E-0B9372A6C704}">
+  <dimension ref="A3:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C3" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C6" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="33"/>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>1</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>2</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>3</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="17"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="17"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
